--- a/results.xlsx
+++ b/results.xlsx
@@ -836,7 +836,7 @@
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] Le document CV est clairement present dans l'extrait 2, intitule cv_martin_dupont.md, qui contient les informations personnelles et professionnelles de Martin Dupont, notamment son profil, son experience et ses competences. [cv_martin_dupont.md, p.1]</t>
+          <t>[HIGH] Le document CV est clairement présent dans l'extrait 1, avec des informations personnelles et professionnelles détaillées, notamment le profil d'ingénieur logiciel avec 4 ans d'expérience en développement Python et architecture cloud. Les extraits 2 et 3, bien que non directement liés au CV, fournissent des informations complémentaires sur la formation académique et les compétences du candidat. [cv_martin_dupont.md, p.1]</t>
         </is>
       </c>
       <c r="J7" s="11">
@@ -881,7 +881,7 @@
       <c r="H8" s="15" t="inlineStr"/>
       <c r="I8" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] La lettre de motivation est clairement presente dans l'extrait 1, avec les details personnels du candidat, Martin Dupont, ainsi que les informations relatives au poste pour lequel il postule. [lettre_motivation.md, p.1]</t>
+          <t>[HIGH] Le document "Lettre de Motivation" est clairement présent dans l'extrait 1, avec les détails tels que l'objet, la candidature, le poste, et la signature du candidat Martin Dupont. Les informations fournies correspondent parfaitement aux exigences d'une lettre de motivation. [lettre_motivation.md, p.1]</t>
         </is>
       </c>
       <c r="J8" s="16">
@@ -926,7 +926,7 @@
       <c r="H9" s="10" t="inlineStr"/>
       <c r="I9" s="29" t="inlineStr">
         <is>
-          <t>[LOW] Aucune pièce d'identité (CNI ou passeport) n'a été trouvée dans les extraits de fichiers fournis. Les documents contiennent des informations sur un contrat de prestation de services et une lettre de recommandation, mais aucun document d'identité n'est présent. [No matching document found]</t>
+          <t>[LOW] Aucun extrait fourni ne correspond clairement à une pièce d'identité (CNI ou passeport). Les extraits trouvés concernent un diplôme, une attestation de droits à l'assurance maladie et un casier judiciaire, mais aucun de ces documents ne remplit les critères d'une pièce d'identité. [No matching document found]</t>
         </is>
       </c>
       <c r="J9" s="11">
@@ -972,7 +972,7 @@
       <c r="H10" s="15" t="inlineStr"/>
       <c r="I10" s="32" t="inlineStr">
         <is>
-          <t>[LOW] Aucun extrait ne contient de mention d'un titre de séjour ou de permis de résidence. Les extraits fournis concernent une politique de sécurité informatique, une lettre de motivation et un contrat de prestation de services, mais aucun d'entre eux ne fait référence à un document de résidence. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne mentionne explicitement un Titre de séjour ou une carte de séjour, les documents trouvés sont une Carte Nationale d'Identite et des contrats de prestation de services, qui ne correspondent pas au document recherché. [No matching document found]</t>
         </is>
       </c>
       <c r="J10" s="16">
@@ -1018,7 +1018,7 @@
       <c r="H11" s="10" t="inlineStr"/>
       <c r="I11" s="32" t="inlineStr">
         <is>
-          <t>[LOW] Aucun extrait fourni ne mentionne explicitement l'autorisation de travail ou tout document similaire. Les extraits semblent provenir d'un règlement intérieur et traitent des horaires de travail, des congés payés et des absences. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne contient d'informations spécifiques sur une autorisation de travail, telles que des dates de début et de fin, un numéro de sécurité sociale, un salaire, des conditions de travail ou des mentions légales. Les extraits semblent être des parties d'un règlement intérieur d'une entreprise, sans lien direct avec un document d'autorisation de travail. [No matching document found]</t>
         </is>
       </c>
       <c r="J11" s="11">
@@ -1063,7 +1063,7 @@
       <c r="H12" s="15" t="inlineStr"/>
       <c r="I12" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] Le numero de securite sociale est presente dans l'extrait 3, fichier contrat_travail_signe.md, page 1, avec le numero 1 95 03 69 123 456 78 pour Monsieur Martin Dupont. [contrat_travail_signe.md, p.1]</t>
+          <t>[HIGH] Le document contient clairement le numéro de Sécurité Sociale (1 95 03 69 123 456 78) ainsi que d'autres informations personnelles telles que la date de naissance et le nom du titulaire, ce qui correspond aux critères de recherche pour un Numéro de Sécurité Sociale / Carte Vitale. [securite_sociale_martin_dupont.md, p.1]</t>
         </is>
       </c>
       <c r="J12" s="16">
@@ -1090,25 +1090,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>❌ Manquant</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>✅ Soumis</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun document pertinent n'a été trouvé dans le dossier candidat, il est donc impossible de déterminer la présence du diplôme ou du certificat. [No matching document found]</t>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>[HIGH] Le document est clairement présent dans l'extrait 1, qui est un diplôme de master en informatique délivré par l'Université Paris-Saclay. Les détails clés tels que le nom du diplôme, la mention, la spécialité et la date de délivrance sont tous présents. [diplome_master_informatique.md, p.1]</t>
         </is>
       </c>
       <c r="J13" s="11">
@@ -1153,7 +1153,7 @@
       <c r="H14" s="15" t="inlineStr"/>
       <c r="I14" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] L'attestation de stage est clairement presente dans l'extrait 1, avec les details suivants : nom du stagiaire (Monsieur DUPONT Martin), dates de stage (du 1er avril 2019 au 30 septembre 2019), et missions realisees. Le document est donc considere comme trouve. [attestation_stage_startupai.md, p.1]</t>
+          <t>[HIGH] L'extrait 1 du fichier attestation_stage_startupai.md contient clairement une attestation de stage pour Monsieur DUPONT Martin, avec les détails du stage, y compris la période, le lieu, les tâches effectuées et l'évaluation du stagiaire. Les informations fournies correspondent aux mots-clés typiques à rechercher pour une attestation de stage. [attestation_stage_startupai.md, p.1]</t>
         </is>
       </c>
       <c r="J14" s="16">
@@ -1198,7 +1198,7 @@
       <c r="H15" s="10" t="inlineStr"/>
       <c r="I15" s="29" t="inlineStr">
         <is>
-          <t>[LOW] Aucun document pertinent n'a été trouvé dans le dossier candidat, il est donc impossible de déterminer si les attestations d'emploi précédents sont présentes. [No matching document found]</t>
+          <t>[LOW] Les extraits fournis ne contiennent pas d'attestation d'emploi précédent. Les documents trouvés sont un contrat de travail et des extraits de règlement intérieur, qui ne correspondent pas au type de document recherché. [No matching document found]</t>
         </is>
       </c>
       <c r="J15" s="11">
@@ -1243,7 +1243,7 @@
       <c r="H16" s="15" t="inlineStr"/>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>[LOW] Aucun justificatif de domicile n'a été trouvé dans les extraits de fichiers fournis. Les extraits semblent être liés à une politique de sécurité informatique et ne contiennent pas d'informations pertinentes pour un justificatif de domicile. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne contient de justificatif de domicile. Les extraits concernent un contrat de travail, un diplôme et un plan de formation, mais aucun d'entre eux ne fournit d'information sur l'adresse du candidat. [No matching document found]</t>
         </is>
       </c>
       <c r="J16" s="16">
@@ -1270,25 +1270,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
-        <is>
-          <t>❌ Manquant</t>
-        </is>
-      </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>✅ Soumis</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun extrait fourni ne contient de relevé d'identité bancaire (RIB) ou de détails de compte bancaire (IBAN). Les extraits semblent être liés à la politique de sécurité informatique et ne mentionnent pas les informations bancaires. [No matching document found]</t>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>[HIGH] Le document Relevé d'Identité Bancaire (RIB) est clairement présent dans l'extrait 1, avec les informations bancaires complètes du titulaire, y compris l'IBAN, le BIC, le code banque, le code guichet, le numéro de compte et la clé RIB. [rib_credit_agricole.md, p.1]</t>
         </is>
       </c>
       <c r="J17" s="11">
@@ -1333,7 +1333,7 @@
       <c r="H18" s="15" t="inlineStr"/>
       <c r="I18" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] L'extrait 1 du fichier casier_judiciaire_b3.md contient clairement un extrait de casier judiciaire B3, avec les informations personnelles du demandeur, le résultat du casier judiciaire et les détails d'authentification. Cependant, il est noté que le document a expiré le 15 janvier 2025. [casier_judiciaire_b3.md, p.1]</t>
+          <t>[HIGH] Le document est clairement présent dans l'extrait 1, avec les mentions "Casier Judiciaire National", "Ministere de la Justice", et les informations personnelles du demandeur, ainsi que le résultat du casier judiciaire. Cependant, il est noté que le document a expiré le 15 janvier 2025. [casier_judiciaire_b3.md, p.1]</t>
         </is>
       </c>
       <c r="J18" s="16">
@@ -1360,25 +1360,25 @@
           <t>Non / No</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>✅ Soumis</t>
-        </is>
-      </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="26" t="inlineStr">
-        <is>
-          <t>[HIGH] La lettre de recommandation est clairement presente dans l'extrait 3, intitulee "lettre_recommandation_techcorp.md", qui contient les details de l'experience de Martin Dupont chez TechCorp Paris et une recommandation formulee par Sophie Marchand, Directrice Technique. [lettre_recommandation_techcorp.md, p.1]</t>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>[LOW] Aucun extrait fourni ne correspond clairement à une lettre de recommandation. Les extraits trouvés incluent un contrat de prestation de services, une lettre de motivation et un diplôme universitaire, mais aucun d'entre eux ne remplit les critères d'une lettre de recommandation. [No matching document found]</t>
         </is>
       </c>
       <c r="J19" s="11">
@@ -1423,7 +1423,7 @@
       <c r="H20" s="15" t="inlineStr"/>
       <c r="I20" s="29" t="inlineStr">
         <is>
-          <t>[LOW] Aucun des extraits fournis ne contient des informations relatives aux résultats de la vérification des antécédents. Les extraits semblent être liés à la politique de sécurité informatique. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne contient des informations relatives aux résultats de la vérification des antécédents, tels que des mentions légales, des informations personnelles ou un historique professionnel. Les extraits se concentrent sur la politique de sécurité informatique, ce qui n'est pas pertinent pour la vérification des antécédents. [No matching document found]</t>
         </is>
       </c>
       <c r="J20" s="16">
@@ -1468,7 +1468,7 @@
       <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="29" t="inlineStr">
         <is>
-          <t>[LOW] Aucun document pertinent n'a été trouvé dans le dossier candidat, il est donc impossible de déterminer si la photo d'identité est présente. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne contient de photo d'identité ou de mention d'une photo d'identité. Les extraits concernent un casier judiciaire, un contrat de travail et un règlement intérieur, mais aucun d'entre eux ne correspond au document recherché, qui est une photo d'identité. [No matching document found]</t>
         </is>
       </c>
       <c r="J21" s="11">
@@ -1513,7 +1513,7 @@
       <c r="H22" s="15" t="inlineStr"/>
       <c r="I22" s="32" t="inlineStr">
         <is>
-          <t>[LOW] Aucune mention d'une carte de visite professionnelle n'a été trouvée dans les extraits de fichiers fournis. Les extraits semblent se concentrer sur la procédure d'accueil des nouveaux collaborateurs. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne correspond clairement a une carte de visite professionnelle. Les extraits concernent des documents relatifs a la securite sociale, a une fiche de contact d'urgence et a une lettre de motivation, mais aucun d'entre eux ne presente les informations typiques d'une carte de visite professionnelle comme le nom, la fonction, la societe, l'adresse, le telephone, l'email, etc. [No matching document found]</t>
         </is>
       </c>
       <c r="J22" s="16">
@@ -1558,7 +1558,7 @@
       <c r="H23" s="10" t="inlineStr"/>
       <c r="I23" s="29" t="inlineStr">
         <is>
-          <t>[LOW] Aucun des extraits fournis ne contient de Convention NDA / Confidentialité. Les documents trouvés incluent un diplôme, un contrat de travail et un contrat de prestation de services, mais aucun d'entre eux ne correspond au document recherché. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne contient de mention explicite d'un accord de non-divulgation (NDA) ou de confidentialité. Les documents trouvés concernent un contrat de travail et un contrat de prestation de services, ainsi qu'un diplôme universitaire, mais aucun d'entre eux ne correspond au type de document recherché. [No matching document found]</t>
         </is>
       </c>
       <c r="J23" s="11">
@@ -1604,7 +1604,7 @@
       <c r="H24" s="15" t="inlineStr"/>
       <c r="I24" s="32" t="inlineStr">
         <is>
-          <t>[LOW] Aucun extrait fourni ne contient de certificat medical d'aptitude. Les extraits proviennent tous d'un plan de formation annuel et ne mentionnent pas de document medical. [No matching document found]</t>
+          <t>[LOW] Aucun des extraits fournis ne contient de certificat médical d'aptitude ou de document similaire. Les extraits proviennent tous d'un règlement intérieur et concernent les horaires de travail, les congés payés et les absences, sans mentionner de certificat médical. [No matching document found]</t>
         </is>
       </c>
       <c r="J24" s="16">
@@ -1631,25 +1631,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E25" s="27" t="inlineStr">
-        <is>
-          <t>❌ Manquant</t>
-        </is>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>✅ Soumis</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="25" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Les extraits fournis ne contiennent pas de contrat de travail signe, mais uniquement des articles du reglement interieur relatifs aux horaires de travail, conges payes et absences. Aucun document specifique portant sur un contrat de travail n'a ete trouve. [No matching document found]</t>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>[HIGH] Le document contient des éléments clés tels que la durée du travail, le lieu de travail, la période d'essai, les obligations de confidentialité et les signatures du salarié et de l'employeur, ce qui correspond clairement à un contrat de travail signé. La date d'entrée en vigueur et les détails sur les parties sont également présents. [contrat_travail_signe.md, p.2]</t>
         </is>
       </c>
       <c r="J25" s="11">
@@ -1694,7 +1694,7 @@
       <c r="H26" s="15" t="inlineStr"/>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] Le document contient clairement les informations de contact d'urgence, y compris les coordonnees de la mere et de la compagne du salarie, ainsi que les informations relatives au medecin traitant. [contact_urgence.md, p.1]</t>
+          <t>[HIGH] Le document contient clairement les informations de contact d'urgence du salarié, y compris les coordonnées de ses contacts principaux et secondaires, ainsi que celles de son médecin traitant. Les détails tels que les noms, prénoms, adresses, numéros de téléphone et adresses e-mail sont présents. [contact_urgence.md, p.1]</t>
         </is>
       </c>
       <c r="J26" s="16">

--- a/results.xlsx
+++ b/results.xlsx
@@ -129,12 +129,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -836,7 +836,7 @@
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] Le document CV est clairement présent dans l'extrait 1, avec des informations personnelles et professionnelles détaillées, notamment le profil d'ingénieur logiciel avec 4 ans d'expérience en développement Python et architecture cloud. Les extraits 2 et 3, bien que non directement liés au CV, fournissent des informations complémentaires sur la formation académique et les compétences du candidat. [cv_martin_dupont.md, p.1]</t>
+          <t>[HIGH] L'extrait 1 provient du fichier cv_martin_dupont.md, page 1, et commence par le titre "Curriculum Vitae". Il comporte les informations typiques d'un CV : date de naissance, adresse, email, téléphone, profil professionnel, expériences et compétences. Le contenu correspond clairement au CV recherché. [cv_martin_dupont.md, p.1]</t>
         </is>
       </c>
       <c r="J7" s="11">
@@ -863,25 +863,25 @@
           <t>Non / No</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>✅ Soumis</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr"/>
-      <c r="I8" s="26" t="inlineStr">
-        <is>
-          <t>[HIGH] Le document "Lettre de Motivation" est clairement présent dans l'extrait 1, avec les détails tels que l'objet, la candidature, le poste, et la signature du candidat Martin Dupont. Les informations fournies correspondent parfaitement aux exigences d'une lettre de motivation. [lettre_motivation.md, p.1]</t>
+      <c r="I8" s="29" t="inlineStr">
+        <is>
+          <t>[LOW] Verdict non déterminé en raison d'une erreur : Error code: 400 - {'error': {'message': "Tool call validation failed: tool call validation failed: parameters for tool DocumentVerdict did not match schema: errors: [missing properties: 'confidence']", 'type': 'invalid_request_error', 'code': 'tool_use_failed', 'failed_generation': '{"name": "DocumentVerdict", "arguments": {\n  "high": "high",\n  "justification": "L\'extrait 1 correspond à une lettre de motivation complète : il comporte l\'objet, la formule d\'appel (Madame), la présentation du candidat, la description de son expérience, la motivation pour le poste, la formule de politesse et la signature. Les dates, le nom du destinataire et le poste visé sont clairement indiqués.",\n  "satisfied": true,\n  "source_file": "lettre_motivation.md",\n  "source_page": 1\n}}'}} [No matching document found]</t>
         </is>
       </c>
       <c r="J8" s="16">
@@ -908,25 +908,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>❌ Manquant</t>
-        </is>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>✅ Soumis</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun extrait fourni ne correspond clairement à une pièce d'identité (CNI ou passeport). Les extraits trouvés concernent un diplôme, une attestation de droits à l'assurance maladie et un casier judiciaire, mais aucun de ces documents ne remplit les critères d'une pièce d'identité. [No matching document found]</t>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>[HIGH] L'extrait 2 contient une Carte Nationale d'Identité (CNI) avec les champs requis : nom, prénoms, date et lieu de naissance, nationalité, numéro de pièce, dates de délivrance et d'expiration, autorité de délivrance, et mention de conformité. Le document correspond clairement à la pièce d'identité recherchée. [dossier_administratif_complet.md, p.47]</t>
         </is>
       </c>
       <c r="J9" s="11">
@@ -954,25 +954,25 @@
 If applicable</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr"/>
-      <c r="I10" s="32" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne mentionne explicitement un Titre de séjour ou une carte de séjour, les documents trouvés sont une Carte Nationale d'Identite et des contrats de prestation de services, qui ne correspondent pas au document recherché. [No matching document found]</t>
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>[LOW] Aucun des extraits fournis ne contient de titre de séjour, carte de séjour ou toute mention de numéro d'identité, dates de délivrance/expiration, autorité délivrante ou autre indicateur d'un titre de séjour. Les documents présentés sont une attestation de droits à l'assurance maladie et des diplômes universitaires, donc le titre de séjour recherché est absent. [No matching document found]</t>
         </is>
       </c>
       <c r="J10" s="16">
@@ -1000,25 +1000,25 @@
 If applicable</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="32" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne contient d'informations spécifiques sur une autorisation de travail, telles que des dates de début et de fin, un numéro de sécurité sociale, un salaire, des conditions de travail ou des mentions légales. Les extraits semblent être des parties d'un règlement intérieur d'une entreprise, sans lien direct avec un document d'autorisation de travail. [No matching document found]</t>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>[HIGH] Les extraits fournis ne contiennent aucun document de type autorisation de travail. Ils ne mentionnent que le règlement intérieur (horaires, congés, absences) sans référence à un titre de séjour, visa, employeur, dates d'émission ou signature d'autorité. [No matching document found]</t>
         </is>
       </c>
       <c r="J11" s="11">
@@ -1063,7 +1063,7 @@
       <c r="H12" s="15" t="inlineStr"/>
       <c r="I12" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] Le document contient clairement le numéro de Sécurité Sociale (1 95 03 69 123 456 78) ainsi que d'autres informations personnelles telles que la date de naissance et le nom du titulaire, ce qui correspond aux critères de recherche pour un Numéro de Sécurité Sociale / Carte Vitale. [securite_sociale_martin_dupont.md, p.1]</t>
+          <t>[MEDIUM] L'extrait 1 contient une attestation de droits à l'Assurance Maladie émise par la CPAM de Paris, incluant le champ "Numero de Securite Sociale" avec la valeur 1 95 03 69 123 456 78. Il s'agit d'une preuve du numéro de sécurité sociale, mais le document n'est pas la Carte Vitale elle‑même (pas d'image ou de mention de la carte). Le numéro est clairement présent, ce qui satisfait partiellement la recherche. [securite_sociale_martin_dupont.md, p.1]</t>
         </is>
       </c>
       <c r="J12" s="16">
@@ -1090,25 +1090,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>✅ Soumis</t>
-        </is>
-      </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
+        <is>
+          <t>❌ Manquant</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="26" t="inlineStr">
-        <is>
-          <t>[HIGH] Le document est clairement présent dans l'extrait 1, qui est un diplôme de master en informatique délivré par l'Université Paris-Saclay. Les détails clés tels que le nom du diplôme, la mention, la spécialité et la date de délivrance sont tous présents. [diplome_master_informatique.md, p.1]</t>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>[LOW] Verdict non déterminé en raison d'une erreur : Error code: 400 - {'error': {'message': "Tool call validation failed: tool call validation failed: parameters for tool DocumentVerdict did not match schema: errors: [missing properties: 'confidence']", 'type': 'invalid_request_error', 'code': 'tool_use_failed', 'failed_generation': '{"name": "DocumentVerdict", "arguments": {\n  "high": "high",\n  "justification": "Les extraits 1 et 2 du fichier diplome_master_informatique.md contiennent le diplôme de Master de Monsieur DUPONT Martin délivré le 15 novembre 2019 par l\'Université Paris‑Saclay, avec numéro d\'enregistrement, mention \\"Très Bien\\", signature du président et sceau de l\'université, correspondant aux critères de diplômes et certificats.",\n  "satisfied": true,\n  "source_file": "diplome_master_informatique.md",\n  "source_page": 1\n}}'}} [No matching document found]</t>
         </is>
       </c>
       <c r="J13" s="11">
@@ -1153,7 +1153,7 @@
       <c r="H14" s="15" t="inlineStr"/>
       <c r="I14" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] L'extrait 1 du fichier attestation_stage_startupai.md contient clairement une attestation de stage pour Monsieur DUPONT Martin, avec les détails du stage, y compris la période, le lieu, les tâches effectuées et l'évaluation du stagiaire. Les informations fournies correspondent aux mots-clés typiques à rechercher pour une attestation de stage. [attestation_stage_startupai.md, p.1]</t>
+          <t>[HIGH] L'extrait 1 correspond à une attestation de stage : il comporte le titre, le nom du stagiaire (Monsieur DUPONT Martin), les dates de début et de fin (1er avril 2019 au 30 septembre 2019), la durée (6 mois), le poste occupé, le tuteur, les missions réalisées, la signature du directeur et le cachet de l'entreprise. Tous les éléments typiques d'une attestation de stage sont présents. [attestation_stage_startupai.md, p.1]</t>
         </is>
       </c>
       <c r="J14" s="16">
@@ -1180,25 +1180,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>❌ Manquant</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Les extraits fournis ne contiennent pas d'attestation d'emploi précédent. Les documents trouvés sont un contrat de travail et des extraits de règlement intérieur, qui ne correspondent pas au type de document recherché. [No matching document found]</t>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>[HIGH] Aucun des extraits ne contient une attestation d'emploi ou un certificat de travail. L'extrait 1 est un contrat de travail signé, incluant des clauses et la date de signature, mais il ne mentionne pas de date d'entrée, de sortie, de poste occupé ou de signature du responsable en tant d'attestation d'emploi. Les extraits 2 et 3 décrivent des procédures d'accueil, sans aucun document de type attestation d'emploi. [No matching document found]</t>
         </is>
       </c>
       <c r="J15" s="11">
@@ -1225,25 +1225,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>❌ Manquant</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H16" s="15" t="inlineStr"/>
-      <c r="I16" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne contient de justificatif de domicile. Les extraits concernent un contrat de travail, un diplôme et un plan de formation, mais aucun d'entre eux ne fournit d'information sur l'adresse du candidat. [No matching document found]</t>
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>[LOW] Aucun des extraits fournis ne contient de document de type justificatif de domicile (facture d'électricité, quittance de loyer, avis d'imposition, etc.). Les extraits portent sur un contrat de prestation, un contrat de travail et un diplôme, sans mention de date de délivrance ou d'adresse du candidat. Ainsi le justificatif de domicile n'est pas présent dans les fichiers disponibles. [No matching document found]</t>
         </is>
       </c>
       <c r="J16" s="16">
@@ -1288,7 +1288,7 @@
       <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] Le document Relevé d'Identité Bancaire (RIB) est clairement présent dans l'extrait 1, avec les informations bancaires complètes du titulaire, y compris l'IBAN, le BIC, le code banque, le code guichet, le numéro de compte et la clé RIB. [rib_credit_agricole.md, p.1]</t>
+          <t>[HIGH] L'extrait 1 contient un Relevé d'Identité Bancaire complet du titulaire DUPONT Martin, avec le code banque, code guichet, numéro de compte, clé RIB, IBAN (FR76 1820 6000 2000 4002 9104 547) et BIC. La date d'émission (05 janvier 2025) est indiquée, ce qui correspond exactement au document recherché. [rib_credit_agricole.md, p.1]</t>
         </is>
       </c>
       <c r="J17" s="11">
@@ -1315,25 +1315,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>✅ Soumis</t>
-        </is>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>❌ Manquant</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G18" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H18" s="15" t="inlineStr"/>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>[HIGH] Le document est clairement présent dans l'extrait 1, avec les mentions "Casier Judiciaire National", "Ministere de la Justice", et les informations personnelles du demandeur, ainsi que le résultat du casier judiciaire. Cependant, il est noté que le document a expiré le 15 janvier 2025. [casier_judiciaire_b3.md, p.1]</t>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>[LOW] Verdict non déterminé en raison d'une erreur : Error code: 400 - {'error': {'message': "Tool call validation failed: tool call validation failed: parameters for tool DocumentVerdict did not match schema: errors: [missing properties: 'confidence']", 'type': 'invalid_request_error', 'code': 'tool_use_failed', 'failed_generation': '{"name": "DocumentVerdict", "arguments": {\n  "high": "high",\n  "justification": "L\'extrait 1 du fichier \'casier_judiciaire_b3.md\' (page 1) correspond exactement à un extrait de casier judiciaire B3 : il comporte le titre BULLETIN N°3, le Ministère de la Justice comme émetteur, les informations d\'identité (Nom DUPONT, Prénom Martin, né le 14/03/1995 à Lyon), la mention d\'absence de condamnation, la date de délivrance du 15 octobre 2024, la référence CJN-2024-10-3847291 et le cachet officiel. Le document est toutefois expiré depuis le 15 janvier 2025, ce qui le rend non valide pour de nouvelles démarches.",\n  "satisfied": true,\n  "source_file": "casier_judiciaire_b3.md",\n  "source_page": 1\n}}'}} [No matching document found]</t>
         </is>
       </c>
       <c r="J18" s="16">
@@ -1360,25 +1360,25 @@
           <t>Non / No</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G19" s="31" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="32" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun extrait fourni ne correspond clairement à une lettre de recommandation. Les extraits trouvés incluent un contrat de prestation de services, une lettre de motivation et un diplôme universitaire, mais aucun d'entre eux ne remplit les critères d'une lettre de recommandation. [No matching document found]</t>
+      <c r="I19" s="29" t="inlineStr">
+        <is>
+          <t>[LOW] Aucun des extraits fournis ne correspond à une lettre de recommandation. Les documents présents sont un contrat de prestation, une lettre de motivation et un diplôme. Aucun texte ne comporte les éléments typiques d'une recommandation (objet, mention de recommandation, coordonnées du référent, signature). [No matching document found]</t>
         </is>
       </c>
       <c r="J19" s="11">
@@ -1405,25 +1405,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>❌ Manquant</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G20" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr"/>
-      <c r="I20" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne contient des informations relatives aux résultats de la vérification des antécédents, tels que des mentions légales, des informations personnelles ou un historique professionnel. Les extraits se concentrent sur la politique de sécurité informatique, ce qui n'est pas pertinent pour la vérification des antécédents. [No matching document found]</t>
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>[HIGH] Aucun des extraits fournis ne contient de document intitulé ou décrivant des résultats de vérification des antécédents, des références professionnelles, un casier judiciaire ou un certificat de bonne conduite. Les extraits portent uniquement sur un diplôme de master et des procédures d'accueil, donc le document recherché est absent. [No matching document found]</t>
         </is>
       </c>
       <c r="J20" s="16">
@@ -1450,25 +1450,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>❌ Manquant</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne contient de photo d'identité ou de mention d'une photo d'identité. Les extraits concernent un casier judiciaire, un contrat de travail et un règlement intérieur, mais aucun d'entre eux ne correspond au document recherché, qui est une photo d'identité. [No matching document found]</t>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>[LOW] Aucun des extraits fournis ne contient de photo d'identité ou toute référence à une image au format passeport. Les documents présentés sont un diplôme, une fiche de contact d'urgence et un extrait de casier judiciaire, aucun ne correspond au type recherché. [No matching document found]</t>
         </is>
       </c>
       <c r="J21" s="11">
@@ -1495,25 +1495,25 @@
           <t>Non / No</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F22" s="31" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G22" s="31" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr"/>
-      <c r="I22" s="32" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne correspond clairement a une carte de visite professionnelle. Les extraits concernent des documents relatifs a la securite sociale, a une fiche de contact d'urgence et a une lettre de motivation, mais aucun d'entre eux ne presente les informations typiques d'une carte de visite professionnelle comme le nom, la fonction, la societe, l'adresse, le telephone, l'email, etc. [No matching document found]</t>
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>[LOW] Aucun des extraits fournis ne contient les informations typiques d'une carte de visite professionnelle (nom, fonction, entreprise, coordonnées, SIREN, etc.). Les documents présentés sont un diplôme, une attestation de sécurité sociale et une lettre de motivation, aucun ne correspond à une carte de visite. [No matching document found]</t>
         </is>
       </c>
       <c r="J22" s="16">
@@ -1540,25 +1540,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>❌ Manquant</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="G23" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="29" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne contient de mention explicite d'un accord de non-divulgation (NDA) ou de confidentialité. Les documents trouvés concernent un contrat de travail et un contrat de prestation de services, ainsi qu'un diplôme universitaire, mais aucun d'entre eux ne correspond au type de document recherché. [No matching document found]</t>
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>[HIGH] Aucun des extraits fournis ne contient de texte correspondant à une convention de confidentialité (NDA). Les documents présentés sont un diplôme de master et un contrat de prestation de services, sans clauses de non-divulgation, signatures d'accord de confidentialité ou mentions similaires. [No matching document found]</t>
         </is>
       </c>
       <c r="J23" s="11">
@@ -1586,25 +1586,25 @@
 If applicable</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F24" s="31" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G24" s="31" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr"/>
-      <c r="I24" s="32" t="inlineStr">
-        <is>
-          <t>[LOW] Aucun des extraits fournis ne contient de certificat médical d'aptitude ou de document similaire. Les extraits proviennent tous d'un règlement intérieur et concernent les horaires de travail, les congés payés et les absences, sans mentionner de certificat médical. [No matching document found]</t>
+      <c r="I24" s="29" t="inlineStr">
+        <is>
+          <t>[LOW] Aucun des extraits fournis ne contient de certificat médical d'aptitude. Les documents présentés sont un diplôme de master et un règlement intérieur mentionnant la nécessité d'un justificatif médical, mais aucun certificat médical réel n'est présent. [No matching document found]</t>
         </is>
       </c>
       <c r="J24" s="16">
@@ -1631,25 +1631,25 @@
           <t>Oui / Yes</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>✅ Soumis</t>
-        </is>
-      </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
+        <is>
+          <t>❌ Manquant</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
         <is>
           <t>AI RAG System</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G25" s="31" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="26" t="inlineStr">
-        <is>
-          <t>[HIGH] Le document contient des éléments clés tels que la durée du travail, le lieu de travail, la période d'essai, les obligations de confidentialité et les signatures du salarié et de l'employeur, ce qui correspond clairement à un contrat de travail signé. La date d'entrée en vigueur et les détails sur les parties sont également présents. [contrat_travail_signe.md, p.2]</t>
+      <c r="I25" s="32" t="inlineStr">
+        <is>
+          <t>[HIGH] Les extraits fournis ne contiennent aucun contrat de travail signé : ils ne présentent que des sections du règlement intérieur (horaires, congés, absences) sans mention de parties, dates de signature, rémunération ou signatures du salarié et de l'employeur. Aucun élément caractéristique d'un contrat d'emploi n'est présent. [No matching document found]</t>
         </is>
       </c>
       <c r="J25" s="11">
@@ -1694,7 +1694,7 @@
       <c r="H26" s="15" t="inlineStr"/>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>[HIGH] Le document contient clairement les informations de contact d'urgence du salarié, y compris les coordonnées de ses contacts principaux et secondaires, ainsi que celles de son médecin traitant. Les détails tels que les noms, prénoms, adresses, numéros de téléphone et adresses e-mail sont présents. [contact_urgence.md, p.1]</t>
+          <t>[HIGH] Le fichier contact_urgence.md, page 1, contient une fiche de contact d'urgence complète avec le nom du salarié (DUPONT Martin), les contacts principaux et secondaires (nom, lien, téléphone, email, adresse), ainsi que le médecin traitant et la signature du salarié datée du 20 mars 2025. Tous les éléments typiques (nom, prénom, relation, téléphone, email, adresse) sont présents. [contact_urgence.md, p.1]</t>
         </is>
       </c>
       <c r="J26" s="16">
